--- a/examples/example_run_generic_excel/experimental_data/raw_data/2026.06.18_ELISA_long_raw.xlsx
+++ b/examples/example_run_generic_excel/experimental_data/raw_data/2026.06.18_ELISA_long_raw.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -979,7 +979,7 @@
         <v>450</v>
       </c>
       <c r="C48">
-        <v>0.2948</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="49">
